--- a/week-01/Abuelita's Coffee House.xlsx
+++ b/week-01/Abuelita's Coffee House.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jessicanavarroservin\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23AC52EB-3218-4AF8-B7A7-39188B03AABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84B6AD2B-7ED3-462C-8D7A-FF9C6484FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Survey Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="20" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="103">
   <si>
     <t>Id</t>
   </si>
@@ -340,9 +340,6 @@
   </si>
   <si>
     <t>How likely are you to return to Abuelita’s Coffee House?</t>
-  </si>
-  <si>
-    <t>=SUM(COUNTIF([How likely are you to return to Abuelita’s Coffee House?], "Somewhat likely"), COUNTIF([How likely are you to return to Abuelita’s Coffee House?], Very likely")</t>
   </si>
   <si>
     <t>Row Labels</t>
@@ -359,8 +356,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -391,33 +388,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="33">
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -437,15 +433,15 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="177" formatCode="0.0"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="177" formatCode="0.0"/>
+      <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -469,13 +465,10 @@
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -527,10 +520,10 @@
       <numFmt numFmtId="28" formatCode="mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="mm/dd/yyyy\ hh:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -654,6 +647,42 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -685,6 +714,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2051-4876-BBDE-505F25472B50}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -698,6 +732,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2051-4876-BBDE-505F25472B50}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -711,6 +750,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2051-4876-BBDE-505F25472B50}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -2594,10 +2638,10 @@
     <cacheField name="Id" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="17"/>
     </cacheField>
-    <cacheField name="Start time" numFmtId="170">
+    <cacheField name="Start time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-09T13:53:15" maxDate="2026-04-10T15:06:40"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="170">
+    <cacheField name="Completion time" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-04-09T13:54:43" maxDate="2026-04-10T15:07:36"/>
     </cacheField>
     <cacheField name="Time To Complete" numFmtId="45">
@@ -3019,12 +3063,138 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5235B9F1-B9A0-45E3-9DE7-AB65B1B31CF2}" name="PivotTable5" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D705CB64-8D2C-41F7-BD3C-8D1B7B99B919}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="4">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5235B9F1-B9A0-45E3-9DE7-AB65B1B31CF2}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="N4:O7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField numFmtId="45" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
@@ -3118,161 +3288,71 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D705CB64-8D2C-41F7-BD3C-8D1B7B99B919}" name="PivotTable4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="17">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField numFmtId="170" showAll="0"/>
-    <pivotField numFmtId="45" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Q19" totalsRowCount="1">
   <autoFilter ref="A1:Q18" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="33" totalsRowDxfId="16">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="32">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="32" totalsRowDxfId="15">
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="31" totalsRowDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="startDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="31" totalsRowDxfId="14">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="30" totalsRowDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitDate"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{4317EC0E-8C85-46AD-8D66-4CA5E04967DB}" name="Time To Complete" totalsRowFunction="custom" dataDxfId="30" totalsRowDxfId="13">
+    <tableColumn id="6" xr3:uid="{4317EC0E-8C85-46AD-8D66-4CA5E04967DB}" name="Time To Complete" totalsRowFunction="custom" dataDxfId="29" totalsRowDxfId="13">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(D2:D18)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="29" totalsRowDxfId="12">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="28" totalsRowDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="28" totalsRowDxfId="11">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="27" totalsRowDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="How old are you?" dataDxfId="27" totalsRowDxfId="10">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="How old are you?" dataDxfId="26" totalsRowDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r47a93a2acc704071842e32f0d7f8d22c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Are you a new customer?" dataDxfId="26" totalsRowDxfId="9">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Are you a new customer?" dataDxfId="25" totalsRowDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r57f86a941d0446598fd9f428a07841ff"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="How much do you usually spend per visit?" dataDxfId="25" totalsRowDxfId="8">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="How much do you usually spend per visit?" dataDxfId="24" totalsRowDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1236c20c2d6847a79f228f74801a7c4d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="How likely are you to recommend us to a friend or colleague?" totalsRowFunction="custom" dataDxfId="24" totalsRowDxfId="7">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="How likely are you to recommend us to a friend or colleague?" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="7">
       <totalsRowFormula>AVERAGE(J2:J18)</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -3280,14 +3360,15 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="How likely are you to return to Abuelita’s Coffee House?" totalsRowLabel="=SUM(COUNTIF([How likely are you to return to Abuelita’s Coffee House?], &quot;Somewhat likely&quot;), COUNTIF([How likely are you to return to Abuelita’s Coffee House?], Very likely&quot;)" dataDxfId="23" totalsRowDxfId="6">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="How likely are you to return to Abuelita’s Coffee House?" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="6">
+      <totalsRowFormula>COUNTIF(OfficeForms.Table[How likely are you to return to Abuelita’s Coffee House?], "Neutral")</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r54f5d64d1e4740aa8f60c92d444812f0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Rate your experience at Abuelita's Coffee House?" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="5">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Rate your experience at Abuelita's Coffee House?" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="5">
       <totalsRowFormula>AVERAGE(L2:L18)</totalsRowFormula>
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
@@ -3295,35 +3376,35 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="What would make your experience at Abuelita’s Coffee House even better?" dataDxfId="21" totalsRowDxfId="4">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="What would make your experience at Abuelita’s Coffee House even better?" dataDxfId="20" totalsRowDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r893a25ce4a214cada8111654a3be559a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="What loyalty program for rewards and discounts are you interested in?" dataDxfId="20" totalsRowDxfId="3">
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="What loyalty program for rewards and discounts are you interested in?" dataDxfId="19" totalsRowDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r2286b16750ad4c6d84fe880b3413bf31"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="What time of day do you most frequent us?" dataDxfId="19" totalsRowDxfId="2">
+    <tableColumn id="35" xr3:uid="{00000000-0010-0000-0000-000023000000}" name="What time of day do you most frequent us?" dataDxfId="18" totalsRowDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r84db5bce278e4369b6ca951d4a341cbe"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="How often do you visit Abuelita’s Coffee House?." dataDxfId="18" totalsRowDxfId="1">
+    <tableColumn id="40" xr3:uid="{00000000-0010-0000-0000-000028000000}" name="How often do you visit Abuelita’s Coffee House?." dataDxfId="17" totalsRowDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re245bdb067f043adbe3a1b46e01b2b18"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Do you visit with friends or family?" dataDxfId="17" totalsRowDxfId="0">
+    <tableColumn id="43" xr3:uid="{00000000-0010-0000-0000-00002B000000}" name="Do you visit with friends or family?" dataDxfId="16" totalsRowDxfId="0">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ree78bdb5deee4e6dbeac013918241e9f"/>
@@ -3687,8 +3768,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="18.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="18.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="31.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -3707,13 +3788,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>98</v>
       </c>
       <c r="E1" t="s">
@@ -3734,7 +3815,7 @@
       <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" t="s">
         <v>99</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -3760,13 +3841,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>46121.578645833331</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>46121.579664351855</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <f t="shared" ref="D2:D18" si="0">C2-B2</f>
         <v>1.0185185237787664E-3</v>
       </c>
@@ -3788,7 +3869,7 @@
       <c r="J2" s="2">
         <v>6</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="2">
@@ -3814,13 +3895,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>46121.581377314818</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>46121.58216435185</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <f t="shared" si="0"/>
         <v>7.8703703184146434E-4</v>
       </c>
@@ -3842,7 +3923,7 @@
       <c r="J3" s="2">
         <v>2</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" t="s">
         <v>29</v>
       </c>
       <c r="L3" s="2">
@@ -3868,13 +3949,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="3">
         <v>46121.581226851849</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>46121.582754629628</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <f t="shared" si="0"/>
         <v>1.527777778392192E-3</v>
       </c>
@@ -3896,7 +3977,7 @@
       <c r="J4" s="2">
         <v>6</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" t="s">
         <v>20</v>
       </c>
       <c r="L4" s="2">
@@ -3922,13 +4003,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="3">
         <v>46121.580104166664</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>46121.583287037036</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <f t="shared" si="0"/>
         <v>3.1828703722567298E-3</v>
       </c>
@@ -3950,7 +4031,7 @@
       <c r="J5" s="2">
         <v>10</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" t="s">
         <v>43</v>
       </c>
       <c r="L5" s="2">
@@ -3976,13 +4057,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>46121.583634259259</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>46121.583969907406</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
         <v>3.3564814657438546E-4</v>
       </c>
@@ -4004,7 +4085,7 @@
       <c r="J6" s="2">
         <v>8</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" t="s">
         <v>43</v>
       </c>
       <c r="L6" s="2">
@@ -4030,13 +4111,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>46121.583495370367</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>46121.584247685183</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <f t="shared" si="0"/>
         <v>7.5231481605442241E-4</v>
       </c>
@@ -4058,7 +4139,7 @@
       <c r="J7" s="2">
         <v>9</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" t="s">
         <v>43</v>
       </c>
       <c r="L7" s="2">
@@ -4084,13 +4165,13 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>46121.582881944443</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>46121.584502314814</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
         <v>1.6203703708015382E-3</v>
       </c>
@@ -4112,7 +4193,7 @@
       <c r="J8" s="2">
         <v>8</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" t="s">
         <v>43</v>
       </c>
       <c r="L8" s="2">
@@ -4138,13 +4219,13 @@
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>46121.584583333337</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>46121.58488425926</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <f t="shared" si="0"/>
         <v>3.0092592351138592E-4</v>
       </c>
@@ -4166,7 +4247,7 @@
       <c r="J9" s="2">
         <v>10</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" t="s">
         <v>61</v>
       </c>
       <c r="L9" s="2">
@@ -4192,13 +4273,13 @@
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>46121.685856481483</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>46121.688854166663</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
         <v>2.9976851801620796E-3</v>
       </c>
@@ -4220,7 +4301,7 @@
       <c r="J10" s="2">
         <v>9</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" t="s">
         <v>20</v>
       </c>
       <c r="L10" s="2">
@@ -4246,13 +4327,13 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>46121.69935185185</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="3">
         <v>46121.701053240744</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <f t="shared" si="0"/>
         <v>1.7013888937071897E-3</v>
       </c>
@@ -4274,7 +4355,7 @@
       <c r="J11" s="2">
         <v>10</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" t="s">
         <v>43</v>
       </c>
       <c r="L11" s="2">
@@ -4300,13 +4381,13 @@
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="3">
         <v>46121.715451388889</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="3">
         <v>46121.726006944446</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
         <v>1.0555555556493346E-2</v>
       </c>
@@ -4328,7 +4409,7 @@
       <c r="J12" s="2">
         <v>7</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" t="s">
         <v>61</v>
       </c>
       <c r="L12" s="2">
@@ -4354,13 +4435,13 @@
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="3">
         <v>46121.739710648151</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>46121.741342592592</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <f t="shared" si="0"/>
         <v>1.631944440305233E-3</v>
       </c>
@@ -4382,7 +4463,7 @@
       <c r="J13" s="2">
         <v>10</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" t="s">
         <v>43</v>
       </c>
       <c r="L13" s="2">
@@ -4408,13 +4489,13 @@
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14" s="3">
         <v>46122.007303240738</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="3">
         <v>46122.009548611109</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
         <v>2.2453703713836148E-3</v>
       </c>
@@ -4436,7 +4517,7 @@
       <c r="J14" s="2">
         <v>10</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" t="s">
         <v>43</v>
       </c>
       <c r="L14" s="2">
@@ -4462,13 +4543,13 @@
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15" s="3">
         <v>46122.432511574072</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>46122.433437500003</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <f t="shared" si="0"/>
         <v>9.2592593136942014E-4</v>
       </c>
@@ -4490,7 +4571,7 @@
       <c r="J15" s="2">
         <v>9</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="2">
@@ -4516,13 +4597,13 @@
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>46122.441944444443</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>46122.442812499998</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
         <v>8.6805555474711582E-4</v>
       </c>
@@ -4544,7 +4625,7 @@
       <c r="J16" s="2">
         <v>6</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" t="s">
         <v>61</v>
       </c>
       <c r="L16" s="2">
@@ -4570,13 +4651,13 @@
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="3">
         <v>46122.604351851849</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="3">
         <v>46122.611620370371</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <f t="shared" si="0"/>
         <v>7.2685185223235749E-3</v>
       </c>
@@ -4598,7 +4679,7 @@
       <c r="J17" s="2">
         <v>7</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K17" t="s">
         <v>20</v>
       </c>
       <c r="L17" s="2">
@@ -4624,13 +4705,13 @@
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="3">
         <v>46122.629629629628</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="3">
         <v>46122.630277777775</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
         <v>6.4814814686542377E-4</v>
       </c>
@@ -4652,7 +4733,7 @@
       <c r="J18" s="2">
         <v>7</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" t="s">
         <v>61</v>
       </c>
       <c r="L18" s="2">
@@ -4675,32 +4756,32 @@
       </c>
     </row>
     <row r="19" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <f>AVERAGE(D2:D18)</f>
         <v>2.2569444447392874E-3</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <f>AVERAGE(J2:J18)</f>
         <v>7.882352941176471</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" s="7">
+      <c r="K19" s="9">
+        <f>COUNTIF(OfficeForms.Table[How likely are you to return to Abuelita’s Coffee House?], "Neutral")</f>
+        <v>4</v>
+      </c>
+      <c r="L19" s="6">
         <f>AVERAGE(L2:L18)</f>
         <v>4.117647058823529</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4739,66 +4820,66 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>101</v>
+      <c r="A3" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="N4" s="9" t="s">
-        <v>101</v>
+      <c r="N4" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="O4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>11</v>
       </c>
-      <c r="N5" s="10" t="s">
+      <c r="N5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B7" s="3">
+      <c r="A7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7">
         <v>17</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" s="3">
+      <c r="N7" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O7">
         <v>17</v>
       </c>
     </row>
